--- a/docs/d/82/inyear.xlsx
+++ b/docs/d/82/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -8818,13 +8818,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L80" s="8" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q104" s="10" t="n">
         <v>2</v>
@@ -11781,7 +11781,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11833,8 +11833,8 @@
       <c r="S109" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T109" s="9" t="n">
-        <v>0</v>
+      <c r="T109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U109" s="9" t="n">
         <v>0</v>
@@ -15164,13 +15164,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>0</v>
       </c>
       <c r="V142" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W142" s="9" t="n">
         <v>0</v>
@@ -15606,7 +15606,7 @@
         <v>4</v>
       </c>
       <c r="Q146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R146" s="9" t="n">
         <v>0</v>
@@ -18735,13 +18735,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
@@ -18780,7 +18780,7 @@
         <v>0</v>
       </c>
       <c r="V177" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W177" s="9" t="n">
         <v>0</v>
@@ -19583,7 +19583,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>

--- a/docs/d/82/inyear.xlsx
+++ b/docs/d/82/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,11 @@
       <c r="AB3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1133,7 +1137,11 @@
       <c r="AB4" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC4" s="4" t="inlineStr"/>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1335,7 +1343,11 @@
       <c r="AB6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1436,7 +1448,11 @@
       <c r="AB7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC7" s="4" t="inlineStr"/>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1537,7 +1553,11 @@
       <c r="AB8" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1945,7 +1965,11 @@
       <c r="AB12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC12" s="4" t="inlineStr"/>
+      <c r="AC12" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -2864,7 +2888,11 @@
       <c r="AB21" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC21" s="4" t="inlineStr"/>
+      <c r="AC21" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -3066,7 +3094,11 @@
       <c r="AB23" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -3167,7 +3199,11 @@
       <c r="AB24" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC24" s="4" t="inlineStr"/>
+      <c r="AC24" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -3777,7 +3813,11 @@
       <c r="AB30" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC30" s="4" t="inlineStr"/>
+      <c r="AC30" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -3983,7 +4023,11 @@
       <c r="AB32" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC32" s="4" t="inlineStr"/>
+      <c r="AC32" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -4395,7 +4439,11 @@
       <c r="AB36" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC36" s="4" t="inlineStr"/>
+      <c r="AC36" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -4706,7 +4754,11 @@
       <c r="AB39" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC39" s="4" t="inlineStr"/>
+      <c r="AC39" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -4807,7 +4859,11 @@
       <c r="AB40" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC40" s="4" t="inlineStr"/>
+      <c r="AC40" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -5114,7 +5170,11 @@
       <c r="AB43" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC43" s="4" t="inlineStr"/>
+      <c r="AC43" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -5215,7 +5275,11 @@
       <c r="AB44" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC44" s="4" t="inlineStr"/>
+      <c r="AC44" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -5623,7 +5687,11 @@
       <c r="AB48" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC48" s="4" t="inlineStr"/>
+      <c r="AC48" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -5724,7 +5792,11 @@
       <c r="AB49" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC49" s="4" t="inlineStr"/>
+      <c r="AC49" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -5825,7 +5897,11 @@
       <c r="AB50" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC50" s="4" t="inlineStr"/>
+      <c r="AC50" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -6233,7 +6309,11 @@
       <c r="AB54" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC54" s="4" t="inlineStr"/>
+      <c r="AC54" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -6536,7 +6616,11 @@
       <c r="AB57" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC57" s="4" t="inlineStr"/>
+      <c r="AC57" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -7053,7 +7137,11 @@
       <c r="AB62" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC62" s="4" t="inlineStr"/>
+      <c r="AC62" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -7255,7 +7343,11 @@
       <c r="AB64" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC64" s="4" t="inlineStr"/>
+      <c r="AC64" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -7461,7 +7553,11 @@
       <c r="AB66" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC66" s="4" t="inlineStr"/>
+      <c r="AC66" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -7768,7 +7864,11 @@
       <c r="AB69" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC69" s="4" t="inlineStr"/>
+      <c r="AC69" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -7970,7 +8070,11 @@
       <c r="AB71" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC71" s="4" t="inlineStr"/>
+      <c r="AC71" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -8172,7 +8276,11 @@
       <c r="AB73" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC73" s="4" t="inlineStr"/>
+      <c r="AC73" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -8374,7 +8482,11 @@
       <c r="AB75" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC75" s="4" t="inlineStr"/>
+      <c r="AC75" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -8782,7 +8894,11 @@
       <c r="AB79" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC79" s="4" t="inlineStr"/>
+      <c r="AC79" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -9295,7 +9411,11 @@
       <c r="AB84" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC84" s="4" t="inlineStr"/>
+      <c r="AC84" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -9497,7 +9617,11 @@
       <c r="AB86" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC86" s="4" t="inlineStr"/>
+      <c r="AC86" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -9598,7 +9722,11 @@
       <c r="AB87" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC87" s="4" t="inlineStr"/>
+      <c r="AC87" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -9804,7 +9932,11 @@
       <c r="AB89" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC89" s="4" t="inlineStr"/>
+      <c r="AC89" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -10317,7 +10449,11 @@
       <c r="AB94" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC94" s="4" t="inlineStr"/>
+      <c r="AC94" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -11141,7 +11277,11 @@
       <c r="AB102" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC102" s="4" t="inlineStr"/>
+      <c r="AC102" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -11242,7 +11382,11 @@
       <c r="AB103" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC103" s="4" t="inlineStr"/>
+      <c r="AC103" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -11343,7 +11487,11 @@
       <c r="AB104" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC104" s="4" t="inlineStr"/>
+      <c r="AC104" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -11549,7 +11697,11 @@
       <c r="AB106" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC106" s="4" t="inlineStr"/>
+      <c r="AC106" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -11860,7 +12012,11 @@
       <c r="AB109" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC109" s="4" t="inlineStr"/>
+      <c r="AC109" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -12167,7 +12323,11 @@
       <c r="AB112" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC112" s="4" t="inlineStr"/>
+      <c r="AC112" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -12268,7 +12428,11 @@
       <c r="AB113" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC113" s="4" t="inlineStr"/>
+      <c r="AC113" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -12878,7 +13042,11 @@
       <c r="AB119" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC119" s="4" t="inlineStr"/>
+      <c r="AC119" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -12979,7 +13147,11 @@
       <c r="AB120" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC120" s="4" t="inlineStr"/>
+      <c r="AC120" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -13290,7 +13462,11 @@
       <c r="AB123" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC123" s="4" t="inlineStr"/>
+      <c r="AC123" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -13391,7 +13567,11 @@
       <c r="AB124" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC124" s="4" t="inlineStr"/>
+      <c r="AC124" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -13803,7 +13983,11 @@
       <c r="AB128" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC128" s="4" t="inlineStr"/>
+      <c r="AC128" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -14009,7 +14193,11 @@
       <c r="AB130" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC130" s="4" t="inlineStr"/>
+      <c r="AC130" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -14110,7 +14298,11 @@
       <c r="AB131" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC131" s="4" t="inlineStr"/>
+      <c r="AC131" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -14413,7 +14605,11 @@
       <c r="AB134" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC134" s="4" t="inlineStr"/>
+      <c r="AC134" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -15439,7 +15635,11 @@
       <c r="AB144" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC144" s="4" t="inlineStr"/>
+      <c r="AC144" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -15641,7 +15841,11 @@
       <c r="AB146" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC146" s="4" t="inlineStr"/>
+      <c r="AC146" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -15742,7 +15946,11 @@
       <c r="AB147" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC147" s="4" t="inlineStr"/>
+      <c r="AC147" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -16457,7 +16665,11 @@
       <c r="AB154" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC154" s="4" t="inlineStr"/>
+      <c r="AC154" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -16558,7 +16770,11 @@
       <c r="AB155" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC155" s="4" t="inlineStr"/>
+      <c r="AC155" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -16764,7 +16980,11 @@
       <c r="AB157" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC157" s="4" t="inlineStr"/>
+      <c r="AC157" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -16865,7 +17085,11 @@
       <c r="AB158" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC158" s="4" t="inlineStr"/>
+      <c r="AC158" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -16966,7 +17190,11 @@
       <c r="AB159" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC159" s="4" t="inlineStr"/>
+      <c r="AC159" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -17479,7 +17707,11 @@
       <c r="AB164" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC164" s="4" t="inlineStr"/>
+      <c r="AC164" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -17681,7 +17913,11 @@
       <c r="AB166" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC166" s="4" t="inlineStr"/>
+      <c r="AC166" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -17782,7 +18018,11 @@
       <c r="AB167" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC167" s="4" t="inlineStr"/>
+      <c r="AC167" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -18089,7 +18329,11 @@
       <c r="AB170" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC170" s="4" t="inlineStr"/>
+      <c r="AC170" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -18190,7 +18434,11 @@
       <c r="AB171" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC171" s="4" t="inlineStr"/>
+      <c r="AC171" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
@@ -18291,7 +18539,11 @@
       <c r="AB172" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC172" s="4" t="inlineStr"/>
+      <c r="AC172" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
@@ -18800,7 +19052,11 @@
       <c r="AB177" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC177" s="4" t="inlineStr"/>
+      <c r="AC177" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AC177"/>

--- a/docs/d/82/inyear.xlsx
+++ b/docs/d/82/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 67 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 63 clubs short</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="P10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="9" t="n">
         <v>1</v>
@@ -3134,13 +3134,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>4</v>
       </c>
       <c r="W24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>7</v>
@@ -3748,13 +3748,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>4</v>
       </c>
       <c r="W30" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X30" s="10" t="n">
         <v>7</v>
@@ -6436,7 +6436,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6506,8 +6506,8 @@
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="10" t="n">
         <v>1</v>
@@ -8005,13 +8005,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>4</v>
       </c>
       <c r="W71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X71" s="10" t="n">
         <v>7</v>
@@ -8110,13 +8110,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8417,13 +8417,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>94</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8464,8 +8464,8 @@
       <c r="V75" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W75" s="9" t="n">
-        <v>3</v>
+      <c r="W75" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X75" s="10" t="n">
         <v>7</v>
@@ -9035,13 +9035,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>0</v>
       </c>
       <c r="V81" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
@@ -9227,7 +9227,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -9297,8 +9297,8 @@
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="9" t="n">
-        <v>0</v>
+      <c r="Z83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="10" t="n">
         <v>1</v>
@@ -9552,13 +9552,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>1</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -10992,7 +10992,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -11033,7 +11033,7 @@
         </is>
       </c>
       <c r="P100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q100" s="9" t="n">
         <v>0</v>
@@ -11044,8 +11044,8 @@
       <c r="S100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T100" s="9" t="n">
-        <v>0</v>
+      <c r="T100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U100" s="9" t="n">
         <v>0</v>
@@ -11212,13 +11212,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>1</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -11659,7 +11659,7 @@
         </is>
       </c>
       <c r="P106" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q106" s="9" t="n">
         <v>0</v>
@@ -12349,7 +12349,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12363,13 +12363,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12407,8 +12407,8 @@
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V113" s="9" t="n">
-        <v>2</v>
+      <c r="V113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -13173,7 +13173,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13243,8 +13243,8 @@
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="9" t="n">
-        <v>0</v>
+      <c r="Z121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA121" s="10" t="n">
         <v>1</v>
@@ -13433,7 +13433,7 @@
         <v>0</v>
       </c>
       <c r="S123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T123" s="9" t="n">
         <v>0</v>
@@ -13502,13 +13502,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>4</v>
       </c>
       <c r="W124" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X124" s="10" t="n">
         <v>7</v>
@@ -14732,7 +14732,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14802,8 +14802,8 @@
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
@@ -15346,7 +15346,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -15360,13 +15360,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -15404,11 +15404,11 @@
       <c r="U142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V142" s="9" t="n">
-        <v>3</v>
+      <c r="V142" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W142" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X142" s="10" t="n">
         <v>7</v>
@@ -16901,7 +16901,7 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -16915,13 +16915,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
@@ -16959,8 +16959,8 @@
       <c r="U157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V157" s="9" t="n">
-        <v>1</v>
+      <c r="V157" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W157" s="9" t="n">
         <v>0</v>
@@ -18369,13 +18369,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>4</v>
       </c>
       <c r="W171" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X171" s="10" t="n">
         <v>7</v>
@@ -18460,7 +18460,7 @@
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>10</v>
@@ -18474,13 +18474,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
@@ -18518,8 +18518,8 @@
       <c r="U172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V172" s="9" t="n">
-        <v>2</v>
+      <c r="V172" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W172" s="9" t="n">
         <v>0</v>
@@ -18973,7 +18973,7 @@
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -18987,13 +18987,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
@@ -19031,8 +19031,8 @@
       <c r="U177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V177" s="9" t="n">
-        <v>3</v>
+      <c r="V177" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W177" s="9" t="n">
         <v>0</v>
@@ -19476,7 +19476,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -19608,7 +19608,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -19674,7 +19674,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -19773,7 +19773,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -19872,7 +19872,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19938,7 +19938,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -20037,7 +20037,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -20070,7 +20070,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -20169,7 +20169,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -20268,7 +20268,7 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -20301,7 +20301,7 @@
         <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>

--- a/docs/d/82/inyear.xlsx
+++ b/docs/d/82/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 63 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1233,8 +1233,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -1278,13 +1278,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>72</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1593,17 +1593,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M9" s="7" t="n">
@@ -1637,11 +1637,11 @@
       <c r="U9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="9" t="n">
-        <v>0</v>
+      <c r="V9" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" s="9" t="n">
         <v>0</v>
@@ -1649,8 +1649,8 @@
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="9" t="n">
-        <v>0</v>
+      <c r="Z9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1694,17 +1694,17 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>9</v>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M10" s="7" t="n">
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="P10" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q10" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R10" s="9" t="n">
         <v>0</v>
@@ -1741,8 +1741,8 @@
       <c r="V10" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W10" s="9" t="n">
-        <v>0</v>
+      <c r="W10" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X10" s="10" t="n">
         <v>7</v>
@@ -1855,8 +1855,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="9" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1956,8 +1956,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2463,8 +2463,8 @@
       <c r="Y17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="9" t="n">
-        <v>0</v>
+      <c r="Z17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA17" s="10" t="n">
         <v>1</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2655,8 +2655,8 @@
       <c r="S19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T19" s="9" t="n">
-        <v>0</v>
+      <c r="T19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U19" s="9" t="n">
         <v>0</v>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2984,8 +2984,8 @@
       <c r="Y22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="9" t="n">
-        <v>0</v>
+      <c r="Z22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA22" s="10" t="n">
         <v>1</v>
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3029,13 +3029,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -3073,11 +3073,11 @@
       <c r="U23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="9" t="n">
-        <v>3</v>
+      <c r="V23" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" s="10" t="n">
         <v>7</v>
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3295,8 +3295,8 @@
       <c r="Y25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
+      <c r="Z25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="10" t="n">
         <v>1</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3340,13 +3340,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3384,11 +3384,11 @@
       <c r="U26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V26" s="9" t="n">
-        <v>0</v>
+      <c r="V26" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X26" s="10" t="n">
         <v>7</v>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3497,8 +3497,8 @@
       <c r="Y27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="9" t="n">
-        <v>0</v>
+      <c r="Z27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="10" t="n">
         <v>1</v>
@@ -3748,13 +3748,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>4</v>
       </c>
       <c r="W30" s="10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="X30" s="10" t="n">
         <v>7</v>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4224,8 +4224,8 @@
       <c r="Y34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z34" s="9" t="n">
-        <v>0</v>
+      <c r="Z34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA34" s="10" t="n">
         <v>1</v>
@@ -4374,13 +4374,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4535,8 +4535,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4640,8 +4640,8 @@
       <c r="Y38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z38" s="9" t="n">
-        <v>0</v>
+      <c r="Z38" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA38" s="10" t="n">
         <v>1</v>
@@ -5402,7 +5402,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5472,8 +5472,8 @@
       <c r="Y46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z46" s="9" t="n">
-        <v>0</v>
+      <c r="Z46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA46" s="10" t="n">
         <v>1</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5521,13 +5521,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -5577,8 +5577,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="P49" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q49" s="9" t="n">
         <v>1</v>
@@ -6024,7 +6024,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6038,13 +6038,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -6082,11 +6082,11 @@
       <c r="U52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V52" s="9" t="n">
-        <v>0</v>
+      <c r="V52" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W52" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X52" s="10" t="n">
         <v>7</v>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6173,7 +6173,7 @@
         <v>2</v>
       </c>
       <c r="Q53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" s="9" t="n">
         <v>0</v>
@@ -6199,8 +6199,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="n">
-        <v>0</v>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6551,13 +6551,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6595,11 +6595,11 @@
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="9" t="n">
-        <v>0</v>
+      <c r="V57" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>7</v>
@@ -6607,8 +6607,8 @@
       <c r="Y57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="9" t="n">
-        <v>0</v>
+      <c r="Z57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="10" t="n">
         <v>1</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -7023,8 +7023,8 @@
       <c r="Y61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z61" s="9" t="n">
-        <v>0</v>
+      <c r="Z61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA61" s="10" t="n">
         <v>1</v>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7233,8 +7233,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -7890,7 +7890,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7960,8 +7960,8 @@
       <c r="Y70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" s="9" t="n">
-        <v>0</v>
+      <c r="Z70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA70" s="10" t="n">
         <v>1</v>
@@ -7991,7 +7991,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -8005,13 +8005,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -8040,8 +8040,8 @@
       <c r="R71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S71" s="9" t="n">
-        <v>1</v>
+      <c r="S71" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T71" s="10" t="n">
         <v>1</v>
@@ -8052,8 +8052,8 @@
       <c r="V71" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W71" s="9" t="n">
-        <v>1</v>
+      <c r="W71" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X71" s="10" t="n">
         <v>7</v>
@@ -8110,13 +8110,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8316,17 +8316,17 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L74" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M74" s="7" t="n">
@@ -8360,11 +8360,11 @@
       <c r="U74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V74" s="9" t="n">
-        <v>1</v>
+      <c r="V74" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X74" s="10" t="n">
         <v>5</v>
@@ -8417,13 +8417,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>94</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8459,13 +8459,13 @@
         <v>1</v>
       </c>
       <c r="U75" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V75" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W75" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X75" s="10" t="n">
         <v>7</v>
@@ -8609,7 +8609,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8679,8 +8679,8 @@
       <c r="Y77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z77" s="9" t="n">
-        <v>0</v>
+      <c r="Z77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA77" s="10" t="n">
         <v>1</v>
@@ -8714,7 +8714,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8784,8 +8784,8 @@
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8829,13 +8829,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -8876,8 +8876,8 @@
       <c r="V79" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W79" s="9" t="n">
-        <v>3</v>
+      <c r="W79" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X79" s="10" t="n">
         <v>7</v>
@@ -8920,7 +8920,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8934,17 +8934,17 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L80" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M80" s="7" t="n">
@@ -8978,11 +8978,11 @@
       <c r="U80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V80" s="9" t="n">
-        <v>3</v>
+      <c r="V80" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X80" s="10" t="n">
         <v>7</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -9035,13 +9035,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
@@ -9079,11 +9079,11 @@
       <c r="U81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V81" s="9" t="n">
-        <v>2</v>
+      <c r="V81" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X81" s="10" t="n">
         <v>7</v>
@@ -9126,7 +9126,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9140,13 +9140,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
@@ -9184,8 +9184,8 @@
       <c r="U82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V82" s="9" t="n">
-        <v>0</v>
+      <c r="V82" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -9196,8 +9196,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -9538,7 +9538,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9552,13 +9552,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9596,11 +9596,11 @@
       <c r="U86" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V86" s="9" t="n">
-        <v>3</v>
+      <c r="V86" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>7</v>
@@ -9762,13 +9762,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>4</v>
       </c>
       <c r="W88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X88" s="10" t="n">
         <v>7</v>
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9867,13 +9867,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9911,11 +9911,11 @@
       <c r="U89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V89" s="9" t="n">
-        <v>0</v>
+      <c r="V89" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>7</v>
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10751,8 +10751,8 @@
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10945,11 +10945,11 @@
       <c r="U99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V99" s="9" t="n">
-        <v>0</v>
+      <c r="V99" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X99" s="10" t="n">
         <v>7</v>
@@ -11093,7 +11093,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11163,8 +11163,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11317,13 +11317,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
@@ -11364,8 +11364,8 @@
       <c r="V103" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W103" s="9" t="n">
-        <v>3</v>
+      <c r="W103" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X103" s="10" t="n">
         <v>7</v>
@@ -11513,7 +11513,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11527,13 +11527,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>0</v>
@@ -11571,11 +11571,11 @@
       <c r="U105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V105" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W105" s="9" t="n">
-        <v>0</v>
+      <c r="V105" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W105" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>7</v>
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11871,14 +11871,14 @@
       <c r="P108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" s="9" t="n">
-        <v>1</v>
+      <c r="Q108" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S108" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T108" s="9" t="n">
         <v>0</v>
@@ -12082,7 +12082,7 @@
         <v>0</v>
       </c>
       <c r="Q110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R110" s="9" t="n">
         <v>0</v>
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12209,8 +12209,8 @@
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
@@ -12244,7 +12244,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12258,13 +12258,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -12302,11 +12302,11 @@
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="9" t="n">
+      <c r="V112" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W112" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="W112" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X112" s="10" t="n">
         <v>7</v>
@@ -12363,13 +12363,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>4</v>
       </c>
       <c r="W113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X113" s="10" t="n">
         <v>7</v>
@@ -12555,7 +12555,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12569,13 +12569,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="8" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12625,8 +12625,8 @@
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -12761,7 +12761,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12831,8 +12831,8 @@
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="9" t="n">
-        <v>0</v>
+      <c r="Z117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -13187,13 +13187,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>4</v>
       </c>
       <c r="W121" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X121" s="10" t="n">
         <v>7</v>
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13292,13 +13292,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -13336,11 +13336,11 @@
       <c r="U122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V122" s="9" t="n">
-        <v>0</v>
+      <c r="V122" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X122" s="10" t="n">
         <v>4</v>
@@ -13348,8 +13348,8 @@
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
@@ -13698,7 +13698,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -13768,8 +13768,8 @@
       <c r="Y126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z126" s="9" t="n">
-        <v>0</v>
+      <c r="Z126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA126" s="10" t="n">
         <v>1</v>
@@ -13799,7 +13799,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13813,17 +13813,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L127" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L127" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M127" s="7" t="n">
@@ -13857,11 +13857,11 @@
       <c r="U127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V127" s="9" t="n">
-        <v>3</v>
+      <c r="V127" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X127" s="10" t="n">
         <v>6</v>
@@ -13869,8 +13869,8 @@
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z127" s="9" t="n">
-        <v>0</v>
+      <c r="Z127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
@@ -13918,13 +13918,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>4</v>
       </c>
       <c r="W128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X128" s="10" t="n">
         <v>7</v>
@@ -14233,13 +14233,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>4</v>
       </c>
       <c r="W131" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X131" s="10" t="n">
         <v>4</v>
@@ -14526,7 +14526,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14596,8 +14596,8 @@
       <c r="Y134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="9" t="n">
-        <v>0</v>
+      <c r="Z134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA134" s="10" t="n">
         <v>1</v>
@@ -15043,7 +15043,7 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -15057,17 +15057,17 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L139" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L139" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M139" s="7" t="n">
@@ -15101,11 +15101,11 @@
       <c r="U139" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V139" s="9" t="n">
-        <v>3</v>
+      <c r="V139" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X139" s="10" t="n">
         <v>7</v>
@@ -15113,8 +15113,8 @@
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="9" t="n">
-        <v>0</v>
+      <c r="Z139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -15451,7 +15451,7 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -15521,8 +15521,8 @@
       <c r="Y143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z143" s="9" t="n">
-        <v>0</v>
+      <c r="Z143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA143" s="10" t="n">
         <v>1</v>
@@ -15556,7 +15556,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -15570,13 +15570,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -15614,11 +15614,11 @@
       <c r="U144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V144" s="9" t="n">
-        <v>1</v>
+      <c r="V144" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W144" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X144" s="10" t="n">
         <v>7</v>
@@ -15661,7 +15661,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -15731,8 +15731,8 @@
       <c r="Y145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z145" s="9" t="n">
-        <v>0</v>
+      <c r="Z145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA145" s="10" t="n">
         <v>1</v>
@@ -16178,7 +16178,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -16248,8 +16248,8 @@
       <c r="Y150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z150" s="9" t="n">
-        <v>0</v>
+      <c r="Z150" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA150" s="10" t="n">
         <v>1</v>
@@ -16600,13 +16600,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>4</v>
       </c>
       <c r="W154" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X154" s="10" t="n">
         <v>7</v>
@@ -16915,13 +16915,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>4</v>
       </c>
       <c r="W157" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X157" s="10" t="n">
         <v>7</v>
@@ -17006,7 +17006,7 @@
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>10</v>
@@ -17076,8 +17076,8 @@
       <c r="Y158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z158" s="9" t="n">
-        <v>0</v>
+      <c r="Z158" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA158" s="10" t="n">
         <v>1</v>
@@ -17216,7 +17216,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -17286,8 +17286,8 @@
       <c r="Y160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z160" s="9" t="n">
-        <v>0</v>
+      <c r="Z160" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA160" s="10" t="n">
         <v>1</v>
@@ -17939,7 +17939,7 @@
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -17953,13 +17953,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
@@ -17997,11 +17997,11 @@
       <c r="U167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V167" s="9" t="n">
-        <v>3</v>
+      <c r="V167" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W167" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X167" s="10" t="n">
         <v>7</v>
@@ -18044,7 +18044,7 @@
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F168" s="6" t="n">
         <v>10</v>
@@ -18058,17 +18058,17 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L168" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L168" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M168" s="7" t="n">
@@ -18102,11 +18102,11 @@
       <c r="U168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V168" s="9" t="n">
-        <v>2</v>
+      <c r="V168" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W168" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X168" s="10" t="n">
         <v>6</v>
@@ -18355,7 +18355,7 @@
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F171" s="6" t="n">
         <v>10</v>
@@ -18369,13 +18369,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         </is>
       </c>
       <c r="P171" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q171" s="9" t="n">
         <v>1</v>
@@ -18405,19 +18405,19 @@
         <v>0</v>
       </c>
       <c r="S171" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T171" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U171" s="9" t="n">
-        <v>0</v>
+      <c r="U171" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V171" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W171" s="9" t="n">
-        <v>3</v>
+      <c r="W171" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X171" s="10" t="n">
         <v>7</v>
@@ -18474,13 +18474,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>4</v>
       </c>
       <c r="W172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X172" s="10" t="n">
         <v>7</v>
@@ -18868,7 +18868,7 @@
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F176" s="6" t="n">
         <v>10</v>
@@ -18882,13 +18882,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
@@ -18926,11 +18926,11 @@
       <c r="U176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V176" s="9" t="n">
-        <v>2</v>
+      <c r="V176" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W176" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X176" s="10" t="n">
         <v>7</v>
@@ -18987,13 +18987,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>4</v>
       </c>
       <c r="W177" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X177" s="10" t="n">
         <v>7</v>
@@ -19146,7 +19146,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -19179,7 +19179,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -19194,7 +19194,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -19212,7 +19212,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -19245,7 +19245,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -19278,7 +19278,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -19344,7 +19344,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -19377,7 +19377,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -19410,7 +19410,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -19443,7 +19443,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -19476,7 +19476,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -19509,7 +19509,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -19542,7 +19542,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -19575,7 +19575,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -19608,7 +19608,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -19623,7 +19623,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -19641,7 +19641,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -19656,7 +19656,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -19674,7 +19674,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -19707,7 +19707,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -19773,7 +19773,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -19806,7 +19806,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -19839,7 +19839,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -19872,7 +19872,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19905,7 +19905,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -19938,7 +19938,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -19971,7 +19971,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -19986,7 +19986,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -20004,7 +20004,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -20037,13 +20037,13 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -20052,7 +20052,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -20070,7 +20070,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -20103,7 +20103,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -20169,7 +20169,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -20235,7 +20235,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -20250,7 +20250,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -20268,13 +20268,13 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -20301,7 +20301,7 @@
         <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>

--- a/docs/d/82/inyear.xlsx
+++ b/docs/d/82/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/82/inyear.xlsx
+++ b/docs/d/82/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/82/inyear.xlsx
+++ b/docs/d/82/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/82/inyear.xlsx
+++ b/docs/d/82/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/82/inyear.xlsx
+++ b/docs/d/82/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$180</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 6 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC179"/>
+  <dimension ref="A1:AC180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -892,13 +892,13 @@
         <v>0</v>
       </c>
       <c r="Q2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" s="9" t="n">
         <v>0</v>
@@ -1278,13 +1278,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>72</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>1</v>
       </c>
       <c r="U8" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V8" s="9" t="n">
         <v>1</v>
@@ -2035,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="9" t="n">
         <v>0</v>
@@ -2306,13 +2306,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
@@ -5004,13 +5004,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -5210,13 +5210,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5756,8 +5756,8 @@
       <c r="P49" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q49" s="9" t="n">
-        <v>1</v>
+      <c r="Q49" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R49" s="9" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
         </is>
       </c>
       <c r="P50" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q50" s="10" t="n">
         <v>2</v>
@@ -7474,7 +7474,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7488,13 +7488,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="P66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q66" s="9" t="n">
         <v>0</v>
@@ -7535,8 +7535,8 @@
       <c r="V66" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W66" s="9" t="n">
-        <v>3</v>
+      <c r="W66" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X66" s="10" t="n">
         <v>7</v>
@@ -8110,13 +8110,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -8459,7 +8459,7 @@
         <v>1</v>
       </c>
       <c r="U75" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V75" s="10" t="n">
         <v>4</v>
@@ -8609,7 +8609,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8623,13 +8623,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8667,8 +8667,8 @@
       <c r="U77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V77" s="9" t="n">
-        <v>2</v>
+      <c r="V77" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="Q79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R79" s="9" t="n">
         <v>0</v>
@@ -9643,7 +9643,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9657,13 +9657,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -9704,8 +9704,8 @@
       <c r="V87" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W87" s="9" t="n">
-        <v>3</v>
+      <c r="W87" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X87" s="10" t="n">
         <v>6</v>
@@ -9958,7 +9958,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9972,13 +9972,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -10016,11 +10016,11 @@
       <c r="U90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V90" s="9" t="n">
-        <v>3</v>
+      <c r="V90" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>5</v>
@@ -10265,7 +10265,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10279,17 +10279,17 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-25</v>
-      </c>
-      <c r="L93" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-3</v>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M93" s="8" t="n">
@@ -10323,11 +10323,11 @@
       <c r="U93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" s="9" t="n">
-        <v>0</v>
+      <c r="V93" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W93" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>6</v>
@@ -10384,13 +10384,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -10489,13 +10489,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11358,8 +11358,8 @@
       <c r="T103" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U103" s="9" t="n">
-        <v>0</v>
+      <c r="U103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V103" s="10" t="n">
         <v>4</v>
@@ -11527,13 +11527,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12668,13 +12668,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12712,8 +12712,8 @@
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="9" t="n">
-        <v>3</v>
+      <c r="V116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -13208,7 +13208,7 @@
         </is>
       </c>
       <c r="P121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q121" s="9" t="n">
         <v>0</v>
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>4</v>
       </c>
       <c r="W122" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X122" s="10" t="n">
         <v>7</v>
@@ -13700,13 +13700,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>4</v>
       </c>
       <c r="W126" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X126" s="10" t="n">
         <v>7</v>
@@ -13910,13 +13910,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14221,13 +14221,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q131" s="9" t="n">
         <v>0</v>
@@ -14265,8 +14265,8 @@
       <c r="U131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V131" s="9" t="n">
-        <v>3</v>
+      <c r="V131" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
@@ -14522,7 +14522,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14574,8 +14574,8 @@
       <c r="S134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T134" s="9" t="n">
-        <v>0</v>
+      <c r="T134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U134" s="9" t="n">
         <v>0</v>
@@ -14615,15 +14615,15 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>28676100</v>
+        <v>3179593</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Rajarata University Toastmasters Club</t>
+          <t>Kekirawa Toastmasters</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14637,25 +14637,25 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L135" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M135" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N135" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O135" s="7" t="inlineStr">
@@ -14681,11 +14681,11 @@
       <c r="U135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="9" t="n">
-        <v>0</v>
+      <c r="V135" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W135" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X135" s="9" t="n">
         <v>0</v>
@@ -14693,14 +14693,14 @@
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA135" s="10" t="n">
-        <v>1</v>
+      <c r="Z135" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA135" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB135" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC135" s="4" t="inlineStr"/>
     </row>
@@ -14716,15 +14716,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>7980472</v>
+        <v>28676100</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>Rajarata University Toastmasters Club</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14738,17 +14738,17 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M136" s="8" t="n">
@@ -14776,38 +14776,34 @@
       <c r="S136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T136" s="10" t="n">
-        <v>1</v>
+      <c r="T136" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V136" s="10" t="n">
-        <v>4</v>
+      <c r="V136" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W136" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X136" s="10" t="n">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="X136" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="10" t="n">
-        <v>1</v>
+      <c r="Z136" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB136" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC136" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC136" s="4" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -14817,19 +14813,19 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>28680140</v>
+        <v>7980472</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>HNB West Cluster Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14843,13 +14839,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14881,8 +14877,8 @@
       <c r="S137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T137" s="9" t="n">
-        <v>0</v>
+      <c r="T137" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U137" s="9" t="n">
         <v>0</v>
@@ -14899,16 +14895,20 @@
       <c r="Y137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z137" s="9" t="n">
-        <v>0</v>
+      <c r="Z137" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA137" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB137" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC137" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC137" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -14922,15 +14922,15 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>7987754</v>
+        <v>28680140</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>HNB West Cluster Toastmasters Club</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14944,13 +14944,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14982,38 +14982,34 @@
       <c r="S138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T138" s="10" t="n">
-        <v>1</v>
+      <c r="T138" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U138" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X138" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="10" t="n">
-        <v>1</v>
+      <c r="Z138" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB138" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC138" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC138" s="4" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -15027,15 +15023,15 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>4278308</v>
+        <v>7987754</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Pinnacle Advanced Toastmasters Club</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -15049,17 +15045,17 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L139" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M139" s="8" t="n">
@@ -15079,7 +15075,7 @@
         <v>0</v>
       </c>
       <c r="Q139" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R139" s="9" t="n">
         <v>0</v>
@@ -15087,14 +15083,14 @@
       <c r="S139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T139" s="9" t="n">
-        <v>0</v>
+      <c r="T139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U139" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
@@ -15112,11 +15108,11 @@
         <v>1</v>
       </c>
       <c r="AB139" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC139" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -15132,15 +15128,15 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>4048942</v>
+        <v>4278308</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Rizing Lanka Toastmasters Club</t>
+          <t>Pinnacle Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -15154,25 +15150,25 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-18</v>
-      </c>
-      <c r="L140" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L140" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M140" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N140" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O140" s="7" t="inlineStr">
@@ -15184,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="Q140" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R140" s="9" t="n">
         <v>0</v>
@@ -15204,22 +15200,26 @@
       <c r="W140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X140" s="9" t="n">
-        <v>0</v>
+      <c r="X140" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z140" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA140" s="9" t="n">
-        <v>0</v>
+      <c r="Z140" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA140" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB140" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC140" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC140" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -15233,15 +15233,15 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>7901236</v>
+        <v>4048942</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Saturday Circle Toastmasters Club</t>
+          <t>Rizing Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -15255,13 +15255,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J141" s="4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>1</v>
+        <v>-18</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -15269,11 +15269,11 @@
         </is>
       </c>
       <c r="M141" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N141" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O141" s="7" t="inlineStr">
@@ -15284,65 +15284,65 @@
       <c r="P141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" s="10" t="n">
-        <v>2</v>
+      <c r="Q141" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R141" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S141" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T141" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U141" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V141" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="T141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V141" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W141" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X141" s="10" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="X141" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA141" s="10" t="n">
-        <v>1</v>
+      <c r="Z141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB141" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AC141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>7975669</v>
+        <v>7901236</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Ceylon Advanced Toastmasters Club</t>
+          <t>Saturday Circle Toastmasters Club</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -15356,13 +15356,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -15385,41 +15385,41 @@
       <c r="P142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" s="9" t="n">
-        <v>0</v>
+      <c r="Q142" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R142" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S142" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T142" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U142" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T142" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U142" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V142" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W142" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X142" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="X142" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z142" s="9" t="n">
-        <v>0</v>
+      <c r="Z142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA142" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB142" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AC142" s="4" t="inlineStr"/>
     </row>
@@ -15435,15 +15435,15 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>777976</v>
+        <v>7975669</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>FTZ Toastmasters Club</t>
+          <t>Ceylon Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -15457,17 +15457,17 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L143" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L143" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M143" s="8" t="n">
@@ -15484,7 +15484,7 @@
         </is>
       </c>
       <c r="P143" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q143" s="9" t="n">
         <v>0</v>
@@ -15501,26 +15501,26 @@
       <c r="U143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V143" s="10" t="n">
-        <v>4</v>
+      <c r="V143" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W143" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X143" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="X143" s="10" t="n">
-        <v>6</v>
-      </c>
       <c r="Y143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z143" s="10" t="n">
-        <v>1</v>
+      <c r="Z143" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA143" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB143" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC143" s="4" t="inlineStr"/>
     </row>
@@ -15536,15 +15536,15 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>7390865</v>
+        <v>777976</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>FTZ Toastmasters Club</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -15558,13 +15558,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -15585,16 +15585,16 @@
         </is>
       </c>
       <c r="P144" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q144" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S144" s="10" t="n">
-        <v>2</v>
+      <c r="S144" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T144" s="9" t="n">
         <v>0</v>
@@ -15605,29 +15605,25 @@
       <c r="V144" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W144" s="10" t="n">
+      <c r="W144" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="X144" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y144" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z144" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA144" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB144" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="X144" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z144" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA144" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB144" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC144" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+      <c r="AC144" s="4" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -15641,15 +15637,15 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>28678062</v>
+        <v>7390865</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>United Tractors Toastmasters Club</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -15663,13 +15659,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
@@ -15690,16 +15686,16 @@
         </is>
       </c>
       <c r="P145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="Q145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S145" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="T145" s="9" t="n">
         <v>0</v>
@@ -15710,8 +15706,8 @@
       <c r="V145" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W145" s="9" t="n">
-        <v>0</v>
+      <c r="W145" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X145" s="10" t="n">
         <v>7</v>
@@ -15746,11 +15742,11 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>1514977</v>
+        <v>28678062</v>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>United Tractors Toastmasters Club</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
@@ -15768,13 +15764,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
@@ -15795,7 +15791,7 @@
         </is>
       </c>
       <c r="P146" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q146" s="9" t="n">
         <v>0</v>
@@ -15816,7 +15812,7 @@
         <v>4</v>
       </c>
       <c r="W146" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X146" s="10" t="n">
         <v>7</v>
@@ -15831,11 +15827,11 @@
         <v>1</v>
       </c>
       <c r="AB146" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC146" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -15847,19 +15843,19 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>28679004</v>
+        <v>1514977</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>IAB Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -15873,13 +15869,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
@@ -15920,8 +15916,8 @@
       <c r="V147" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W147" s="10" t="n">
-        <v>4</v>
+      <c r="W147" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="X147" s="10" t="n">
         <v>7</v>
@@ -15936,9 +15932,13 @@
         <v>1</v>
       </c>
       <c r="AB147" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC147" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC147" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -15952,11 +15952,11 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>1818104</v>
+        <v>28679004</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>IAB Toastmasters Club</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
@@ -15974,13 +15974,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="J148" s="4" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>-11</v>
+        <v>-5</v>
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
@@ -16000,11 +16000,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P148" s="10" t="n">
-        <v>4</v>
+      <c r="P148" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q148" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R148" s="9" t="n">
         <v>0</v>
@@ -16021,8 +16021,8 @@
       <c r="V148" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W148" s="9" t="n">
-        <v>1</v>
+      <c r="W148" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X148" s="10" t="n">
         <v>7</v>
@@ -16037,13 +16037,9 @@
         <v>1</v>
       </c>
       <c r="AB148" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC148" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -16057,15 +16053,15 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>1378886</v>
+        <v>1818104</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -16079,13 +16075,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
@@ -16105,8 +16101,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P149" s="9" t="n">
-        <v>3</v>
+      <c r="P149" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q149" s="9" t="n">
         <v>1</v>
@@ -16115,19 +16111,19 @@
         <v>0</v>
       </c>
       <c r="S149" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T149" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U149" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T149" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U149" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V149" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W149" s="10" t="n">
-        <v>4</v>
+      <c r="W149" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="X149" s="10" t="n">
         <v>7</v>
@@ -16162,15 +16158,15 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>7391111</v>
+        <v>1378886</v>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Puttalam Toastmasters</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -16184,17 +16180,17 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L150" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M150" s="8" t="n">
@@ -16210,46 +16206,50 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P150" s="9" t="n">
-        <v>0</v>
+      <c r="P150" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R150" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S150" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T150" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U150" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V150" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W150" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X150" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T150" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U150" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V150" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W150" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X150" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z150" s="9" t="n">
-        <v>0</v>
+      <c r="Z150" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA150" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB150" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC150" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC150" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -16263,15 +16263,15 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>1055854</v>
+        <v>7391111</v>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Wayamba Toastmasters</t>
+          <t>Puttalam Toastmasters</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -16285,17 +16285,17 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L151" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L151" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M151" s="8" t="n">
@@ -16312,7 +16312,7 @@
         </is>
       </c>
       <c r="P151" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q151" s="9" t="n">
         <v>0</v>
@@ -16329,32 +16329,28 @@
       <c r="U151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V151" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W151" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="X151" s="10" t="n">
-        <v>6</v>
+      <c r="V151" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W151" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z151" s="10" t="n">
-        <v>1</v>
+      <c r="Z151" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA151" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB151" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC151" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC151" s="4" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -16368,15 +16364,15 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>28680382</v>
+        <v>1055854</v>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Wennappuwa Toastmasters Club</t>
+          <t>Wayamba Toastmasters</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -16390,13 +16386,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
@@ -16417,7 +16413,7 @@
         </is>
       </c>
       <c r="P152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q152" s="9" t="n">
         <v>0</v>
@@ -16434,28 +16430,32 @@
       <c r="U152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V152" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W152" s="9" t="n">
-        <v>0</v>
+      <c r="V152" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W152" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X152" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y152" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z152" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA152" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB152" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Y152" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z152" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA152" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB152" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC152" s="4" t="inlineStr"/>
+      <c r="AC152" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -16465,19 +16465,19 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>7855253</v>
+        <v>28680382</v>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Ampara Toastmasters Club</t>
+          <t>Wennappuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -16491,17 +16491,17 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L153" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L153" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M153" s="8" t="n">
@@ -16542,25 +16542,21 @@
         <v>0</v>
       </c>
       <c r="X153" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z153" s="9" t="n">
-        <v>0</v>
+      <c r="Z153" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA153" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB153" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC153" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC153" s="4" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -16574,11 +16570,11 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>28675349</v>
+        <v>7855253</v>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Ansell Textiles Lanka Toastmasters Club</t>
+          <t>Ampara Toastmasters Club</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
@@ -16596,13 +16592,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>-11</v>
+        <v>-7</v>
       </c>
       <c r="L154" s="7" t="inlineStr">
         <is>
@@ -16632,7 +16628,7 @@
         <v>0</v>
       </c>
       <c r="S154" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T154" s="9" t="n">
         <v>0</v>
@@ -16641,13 +16637,13 @@
         <v>0</v>
       </c>
       <c r="V154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W154" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X154" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y154" s="9" t="n">
         <v>0</v>
@@ -16659,9 +16655,13 @@
         <v>1</v>
       </c>
       <c r="AB154" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC154" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC154" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -16675,15 +16675,15 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>28680546</v>
+        <v>28675349</v>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Chilaw Toastmasters Club</t>
+          <t>Ansell Textiles Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -16697,17 +16697,17 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K155" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L155" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L155" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M155" s="8" t="n">
@@ -16733,7 +16733,7 @@
         <v>0</v>
       </c>
       <c r="S155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T155" s="9" t="n">
         <v>0</v>
@@ -16741,26 +16741,26 @@
       <c r="U155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V155" s="9" t="n">
+      <c r="V155" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W155" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="W155" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="X155" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z155" s="9" t="n">
-        <v>0</v>
+      <c r="Z155" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA155" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB155" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC155" s="4" t="inlineStr"/>
     </row>
@@ -16776,15 +16776,15 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>6604478</v>
+        <v>28680546</v>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Chilaw Toastmasters Club</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -16801,10 +16801,10 @@
         <v>22</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
@@ -16842,11 +16842,11 @@
       <c r="U156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V156" s="10" t="n">
-        <v>4</v>
+      <c r="V156" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W156" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X156" s="10" t="n">
         <v>7</v>
@@ -16854,20 +16854,16 @@
       <c r="Y156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z156" s="10" t="n">
-        <v>1</v>
+      <c r="Z156" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA156" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB156" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC156" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -16881,15 +16877,15 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>28675770</v>
+        <v>6604478</v>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -16903,13 +16899,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="J157" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>7</v>
+        <v>-5</v>
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
@@ -16950,8 +16946,8 @@
       <c r="V157" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W157" s="10" t="n">
-        <v>5</v>
+      <c r="W157" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="X157" s="10" t="n">
         <v>7</v>
@@ -16982,19 +16978,19 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>5144557</v>
+        <v>28675770</v>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>10</v>
@@ -17008,17 +17004,17 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="J158" s="4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L158" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>7</v>
+      </c>
+      <c r="L158" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M158" s="8" t="n">
@@ -17052,11 +17048,11 @@
       <c r="U158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V158" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W158" s="9" t="n">
-        <v>0</v>
+      <c r="V158" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W158" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X158" s="10" t="n">
         <v>7</v>
@@ -17075,7 +17071,7 @@
       </c>
       <c r="AC158" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -17091,15 +17087,15 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>7832471</v>
+        <v>5144557</v>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -17113,17 +17109,17 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L159" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L159" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M159" s="8" t="n">
@@ -17140,28 +17136,28 @@
         </is>
       </c>
       <c r="P159" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q159" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S159" s="10" t="n">
+      <c r="S159" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T159" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U159" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V159" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="T159" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U159" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V159" s="10" t="n">
-        <v>4</v>
-      </c>
       <c r="W159" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X159" s="10" t="n">
         <v>7</v>
@@ -17180,7 +17176,7 @@
       </c>
       <c r="AC159" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -17196,15 +17192,15 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>7856786</v>
+        <v>7832471</v>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -17218,17 +17214,17 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J160" s="4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L160" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L160" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M160" s="8" t="n">
@@ -17245,31 +17241,31 @@
         </is>
       </c>
       <c r="P160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S160" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T160" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U160" s="10" t="n">
-        <v>1</v>
+      <c r="S160" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U160" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V160" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W160" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X160" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y160" s="9" t="n">
         <v>0</v>
@@ -17301,15 +17297,15 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>7639</v>
+        <v>7856786</v>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>10</v>
@@ -17323,17 +17319,17 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L161" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L161" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M161" s="8" t="n">
@@ -17349,32 +17345,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P161" s="10" t="n">
+      <c r="P161" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U161" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V161" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q161" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R161" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S161" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T161" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U161" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V161" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="W161" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X161" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y161" s="9" t="n">
         <v>0</v>
@@ -17406,15 +17402,15 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>3200777</v>
+        <v>7639</v>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Sunday Live Speakers Forum</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F162" s="6" t="n">
         <v>10</v>
@@ -17428,17 +17424,17 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K162" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L162" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L162" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M162" s="8" t="n">
@@ -17454,32 +17450,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P162" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q162" s="10" t="n">
+      <c r="P162" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q162" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R162" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V162" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R162" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S162" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T162" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U162" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V162" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="W162" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X162" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y162" s="9" t="n">
         <v>0</v>
@@ -17491,31 +17487,35 @@
         <v>1</v>
       </c>
       <c r="AB162" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC162" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC162" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>7855572</v>
+        <v>3200777</v>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Capital Toastmasters Club</t>
+          <t>Sunday Live Speakers Forum</t>
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -17529,17 +17529,17 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J163" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L163" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L163" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M163" s="8" t="n">
@@ -17558,14 +17558,14 @@
       <c r="P163" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q163" s="9" t="n">
-        <v>0</v>
+      <c r="Q163" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R163" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S163" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T163" s="10" t="n">
         <v>1</v>
@@ -17574,13 +17574,13 @@
         <v>0</v>
       </c>
       <c r="V163" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W163" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X163" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y163" s="9" t="n">
         <v>0</v>
@@ -17592,13 +17592,9 @@
         <v>1</v>
       </c>
       <c r="AB163" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC163" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="AC163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
@@ -17612,15 +17608,15 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>4903005</v>
+        <v>7855572</v>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
+          <t>Capital Toastmasters Club</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>10</v>
@@ -17634,17 +17630,17 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L164" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L164" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M164" s="8" t="n">
@@ -17661,7 +17657,7 @@
         </is>
       </c>
       <c r="P164" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q164" s="9" t="n">
         <v>0</v>
@@ -17672,14 +17668,14 @@
       <c r="S164" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T164" s="9" t="n">
-        <v>0</v>
+      <c r="T164" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U164" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V164" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W164" s="9" t="n">
         <v>0</v>
@@ -17697,11 +17693,11 @@
         <v>1</v>
       </c>
       <c r="AB164" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC164" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -17717,15 +17713,15 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>28678414</v>
+        <v>4903005</v>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Codegen Toastmasters</t>
+          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -17739,13 +17735,13 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J165" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
@@ -17753,11 +17749,11 @@
         </is>
       </c>
       <c r="M165" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N165" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O165" s="7" t="inlineStr">
@@ -17775,7 +17771,7 @@
         <v>0</v>
       </c>
       <c r="S165" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T165" s="9" t="n">
         <v>0</v>
@@ -17789,22 +17785,26 @@
       <c r="W165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X165" s="9" t="n">
-        <v>0</v>
+      <c r="X165" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z165" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA165" s="9" t="n">
-        <v>0</v>
+      <c r="Z165" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA165" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB165" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC165" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC165" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
@@ -17818,98 +17818,94 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>2302941</v>
+        <v>28678414</v>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Expolanka Toastmasters Club</t>
+          <t>Codegen Toastmasters</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G166" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I166" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M166" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N166" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O166" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB166" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F166" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G166" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I166" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="J166" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="K166" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L166" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M166" s="8" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N166" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O166" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P166" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q166" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R166" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S166" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T166" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U166" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V166" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W166" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X166" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y166" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z166" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA166" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB166" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC166" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AC166" s="4" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -17923,15 +17919,15 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>7287138</v>
+        <v>2302941</v>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Maharagama Toastmasters</t>
+          <t>Expolanka Toastmasters Club</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -17945,13 +17941,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="J167" s="4" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
@@ -17972,7 +17968,7 @@
         </is>
       </c>
       <c r="P167" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q167" s="9" t="n">
         <v>0</v>
@@ -17983,8 +17979,8 @@
       <c r="S167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T167" s="10" t="n">
-        <v>1</v>
+      <c r="T167" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U167" s="9" t="n">
         <v>0</v>
@@ -17992,11 +17988,11 @@
       <c r="V167" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W167" s="10" t="n">
-        <v>9</v>
+      <c r="W167" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="X167" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y167" s="9" t="n">
         <v>0</v>
@@ -18008,9 +18004,13 @@
         <v>1</v>
       </c>
       <c r="AB167" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC167" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC167" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -18020,15 +18020,15 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>2321352</v>
+        <v>7287138</v>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Aitken Spence Toastmasters</t>
+          <t>Maharagama Toastmasters</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
@@ -18046,13 +18046,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="J168" s="4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         </is>
       </c>
       <c r="P168" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q168" s="9" t="n">
         <v>0</v>
@@ -18094,10 +18094,10 @@
         <v>4</v>
       </c>
       <c r="W168" s="10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="X168" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y168" s="9" t="n">
         <v>0</v>
@@ -18109,13 +18109,9 @@
         <v>1</v>
       </c>
       <c r="AB168" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC168" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="AC168" s="4" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -18129,15 +18125,15 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>4091394</v>
+        <v>2321352</v>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Ceylinco Life Toastmasters Club</t>
+          <t>Aitken Spence Toastmasters</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F169" s="6" t="n">
         <v>10</v>
@@ -18151,13 +18147,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
@@ -18198,8 +18194,8 @@
       <c r="V169" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W169" s="9" t="n">
-        <v>1</v>
+      <c r="W169" s="10" t="n">
+        <v>14</v>
       </c>
       <c r="X169" s="10" t="n">
         <v>7</v>
@@ -18234,39 +18230,39 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>7959271</v>
+        <v>4091394</v>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Improvers Toastmasters Club</t>
+          <t>Ceylinco Life Toastmasters Club</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F170" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G170" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I170" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="J170" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="K170" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F170" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G170" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H170" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I170" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="J170" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K170" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L170" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L170" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M170" s="8" t="n">
@@ -18283,10 +18279,10 @@
         </is>
       </c>
       <c r="P170" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q170" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R170" s="9" t="n">
         <v>0</v>
@@ -18294,8 +18290,8 @@
       <c r="S170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T170" s="9" t="n">
-        <v>0</v>
+      <c r="T170" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U170" s="9" t="n">
         <v>0</v>
@@ -18307,7 +18303,7 @@
         <v>1</v>
       </c>
       <c r="X170" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y170" s="9" t="n">
         <v>0</v>
@@ -18319,9 +18315,13 @@
         <v>1</v>
       </c>
       <c r="AB170" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC170" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC170" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -18335,15 +18335,15 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>7966661</v>
+        <v>7959271</v>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+          <t>Improvers Toastmasters Club</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F171" s="6" t="n">
         <v>10</v>
@@ -18357,17 +18357,17 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J171" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L171" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L171" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M171" s="8" t="n">
@@ -18384,10 +18384,10 @@
         </is>
       </c>
       <c r="P171" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q171" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R171" s="9" t="n">
         <v>0</v>
@@ -18401,32 +18401,28 @@
       <c r="U171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V171" s="9" t="n">
-        <v>1</v>
+      <c r="V171" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W171" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X171" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y171" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z171" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA171" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB171" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="Y171" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z171" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA171" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB171" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC171" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+      <c r="AC171" s="4" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
@@ -18436,19 +18432,19 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>7794099</v>
+        <v>7966661</v>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Central Link Toastmasters Club</t>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>10</v>
@@ -18462,17 +18458,17 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="J172" s="4" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L172" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L172" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M172" s="8" t="n">
@@ -18489,7 +18485,7 @@
         </is>
       </c>
       <c r="P172" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q172" s="9" t="n">
         <v>0</v>
@@ -18506,14 +18502,14 @@
       <c r="U172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V172" s="10" t="n">
-        <v>4</v>
+      <c r="V172" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W172" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X172" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y172" s="9" t="n">
         <v>0</v>
@@ -18529,7 +18525,7 @@
       </c>
       <c r="AC172" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -18545,15 +18541,15 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>6650357</v>
+        <v>7794099</v>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Dowels Toastmasters Club</t>
+          <t>Central Link Toastmasters Club</t>
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F173" s="6" t="n">
         <v>10</v>
@@ -18567,13 +18563,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J173" s="4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
@@ -18594,28 +18590,28 @@
         </is>
       </c>
       <c r="P173" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q173" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R173" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S173" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T173" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U173" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T173" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U173" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V173" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W173" s="10" t="n">
-        <v>8</v>
+      <c r="W173" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="X173" s="10" t="n">
         <v>7</v>
@@ -18650,35 +18646,35 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>6602877</v>
+        <v>6650357</v>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Kegalle Toastmasters Club</t>
+          <t>Dowels Toastmasters Club</t>
         </is>
       </c>
       <c r="E174" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F174" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G174" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I174" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="J174" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="K174" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F174" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G174" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H174" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I174" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="J174" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="K174" s="4" t="n">
-        <v>-4</v>
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
@@ -18699,10 +18695,10 @@
         </is>
       </c>
       <c r="P174" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q174" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R174" s="9" t="n">
         <v>0</v>
@@ -18710,17 +18706,17 @@
       <c r="S174" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T174" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U174" s="9" t="n">
-        <v>0</v>
+      <c r="T174" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U174" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V174" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W174" s="9" t="n">
-        <v>1</v>
+      <c r="W174" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X174" s="10" t="n">
         <v>7</v>
@@ -18755,15 +18751,15 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>7913101</v>
+        <v>6602877</v>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Peradeniya University Toastmasters Club</t>
+          <t>Kegalle Toastmasters Club</t>
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -18777,17 +18773,17 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J175" s="4" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L175" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-4</v>
+      </c>
+      <c r="L175" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M175" s="8" t="n">
@@ -18804,31 +18800,31 @@
         </is>
       </c>
       <c r="P175" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q175" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q175" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R175" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S175" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R175" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S175" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="T175" s="9" t="n">
         <v>0</v>
       </c>
       <c r="U175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V175" s="9" t="n">
-        <v>2</v>
+      <c r="V175" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W175" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X175" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y175" s="9" t="n">
         <v>0</v>
@@ -18840,9 +18836,13 @@
         <v>1</v>
       </c>
       <c r="AB175" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC175" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC175" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
@@ -18852,19 +18852,19 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>28679036</v>
+        <v>7913101</v>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Esoft Uni Kandy Toastmasters Club</t>
+          <t>Peradeniya University Toastmasters Club</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F176" s="6" t="n">
         <v>10</v>
@@ -18878,13 +18878,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J176" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="L176" s="7" t="inlineStr">
         <is>
@@ -18905,13 +18905,13 @@
         </is>
       </c>
       <c r="P176" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q176" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="Q176" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R176" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S176" s="9" t="n">
         <v>0</v>
@@ -18923,25 +18923,25 @@
         <v>0</v>
       </c>
       <c r="V176" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W176" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X176" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z176" s="9" t="n">
-        <v>0</v>
+      <c r="Z176" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA176" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB176" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC176" s="4" t="inlineStr"/>
     </row>
@@ -18957,11 +18957,11 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>28678629</v>
+        <v>28679036</v>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>IESL Kandurata Chapter Toastmasters Club</t>
+          <t>Esoft Uni Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="E177" s="5" t="n">
@@ -18979,13 +18979,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
@@ -19006,10 +19006,10 @@
         </is>
       </c>
       <c r="P177" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q177" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R177" s="9" t="n">
         <v>0</v>
@@ -19030,7 +19030,7 @@
         <v>0</v>
       </c>
       <c r="X177" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y177" s="9" t="n">
         <v>0</v>
@@ -19042,7 +19042,7 @@
         <v>1</v>
       </c>
       <c r="AB177" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC177" s="4" t="inlineStr"/>
     </row>
@@ -19058,15 +19058,15 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>7232170</v>
+        <v>28678629</v>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Kandy Lions Toastmasters Club</t>
+          <t>IESL Kandurata Chapter Toastmasters Club</t>
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>10</v>
@@ -19080,13 +19080,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J178" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="L178" s="7" t="inlineStr">
         <is>
@@ -19118,38 +19118,34 @@
       <c r="S178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T178" s="10" t="n">
-        <v>1</v>
+      <c r="T178" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V178" s="10" t="n">
-        <v>4</v>
+      <c r="V178" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W178" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X178" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z178" s="10" t="n">
-        <v>1</v>
+      <c r="Z178" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA178" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB178" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC178" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC178" s="4" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
@@ -19163,11 +19159,11 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>822324</v>
+        <v>7232170</v>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>Kandy Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
@@ -19185,17 +19181,17 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J179" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L179" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L179" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M179" s="8" t="n">
@@ -19212,7 +19208,7 @@
         </is>
       </c>
       <c r="P179" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q179" s="9" t="n">
         <v>0</v>
@@ -19221,7 +19217,7 @@
         <v>0</v>
       </c>
       <c r="S179" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T179" s="10" t="n">
         <v>1</v>
@@ -19233,7 +19229,7 @@
         <v>4</v>
       </c>
       <c r="W179" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X179" s="10" t="n">
         <v>7</v>
@@ -19248,16 +19244,121 @@
         <v>1</v>
       </c>
       <c r="AB179" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC179" s="4" t="inlineStr">
         <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="n">
+        <v>822324</v>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>Kandy Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E180" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F180" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G180" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I180" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="J180" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K180" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L180" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M180" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N180" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O180" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P180" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q180" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R180" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S180" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T180" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U180" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V180" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W180" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X180" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y180" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z180" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA180" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB180" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC180" s="4" t="inlineStr">
+        <is>
           <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC179"/>
+  <autoFilter ref="A1:AC180"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19641,7 +19742,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -19740,7 +19841,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -19806,7 +19907,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -19905,7 +20006,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -19938,7 +20039,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -19953,7 +20054,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -20004,13 +20105,13 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -20103,7 +20204,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -20169,7 +20270,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -20199,22 +20300,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>2</v>
@@ -20301,7 +20402,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -20334,7 +20435,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -20448,7 +20549,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -20466,7 +20567,7 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -20499,7 +20600,7 @@
         <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>

--- a/docs/d/82/inyear.xlsx
+++ b/docs/d/82/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 6 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 6 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="P3" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="9" t="n">
         <v>0</v>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1113,8 +1113,8 @@
       <c r="T4" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U4" s="9" t="n">
-        <v>0</v>
+      <c r="U4" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V4" s="10" t="n">
         <v>4</v>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="P7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="9" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1732,8 +1732,8 @@
       <c r="S10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T10" s="9" t="n">
-        <v>0</v>
+      <c r="T10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U10" s="9" t="n">
         <v>0</v>
@@ -2306,13 +2306,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" s="9" t="n">
         <v>0</v>
@@ -3029,13 +3029,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>4</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X23" s="10" t="n">
         <v>7</v>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3748,13 +3748,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="P30" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q30" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="Q30" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R30" s="9" t="n">
         <v>0</v>
@@ -3796,7 +3796,7 @@
         <v>4</v>
       </c>
       <c r="W30" s="10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X30" s="10" t="n">
         <v>7</v>
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="P32" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q32" s="9" t="n">
         <v>0</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="P39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>0</v>
@@ -4727,8 +4727,8 @@
       <c r="S39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T39" s="9" t="n">
-        <v>0</v>
+      <c r="T39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U39" s="9" t="n">
         <v>0</v>
@@ -5608,7 +5608,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5660,8 +5660,8 @@
       <c r="S48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T48" s="9" t="n">
-        <v>0</v>
+      <c r="T48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U48" s="9" t="n">
         <v>0</v>
@@ -7072,13 +7072,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -7305,13 +7305,13 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q64" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S64" s="9" t="n">
         <v>1</v>
@@ -7410,7 +7410,7 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q65" s="9" t="n">
         <v>1</v>
@@ -7488,13 +7488,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>4</v>
       </c>
       <c r="W66" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X66" s="10" t="n">
         <v>7</v>
@@ -7835,7 +7835,7 @@
         <v>0</v>
       </c>
       <c r="S69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T69" s="9" t="n">
         <v>0</v>
@@ -10205,7 +10205,7 @@
         </is>
       </c>
       <c r="P92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q92" s="9" t="n">
         <v>0</v>
@@ -10823,7 +10823,7 @@
         </is>
       </c>
       <c r="P98" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q98" s="9" t="n">
         <v>0</v>
@@ -11093,7 +11093,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11137,7 +11137,7 @@
         <v>3</v>
       </c>
       <c r="Q101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" s="9" t="n">
         <v>0</v>
@@ -11145,8 +11145,8 @@
       <c r="S101" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T101" s="9" t="n">
-        <v>0</v>
+      <c r="T101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U101" s="9" t="n">
         <v>0</v>
@@ -12492,7 +12492,7 @@
         <v>1</v>
       </c>
       <c r="Q114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R114" s="9" t="n">
         <v>0</v>
@@ -13103,7 +13103,7 @@
         </is>
       </c>
       <c r="P120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q120" s="9" t="n">
         <v>0</v>
@@ -13910,13 +13910,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -14011,13 +14011,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         </is>
       </c>
       <c r="P130" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q130" s="9" t="n">
         <v>0</v>
@@ -14693,8 +14693,8 @@
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="10" t="n">
-        <v>2</v>
+      <c r="Z135" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA135" s="9" t="n">
         <v>0</v>
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14875,13 +14875,13 @@
         <v>0</v>
       </c>
       <c r="S137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T137" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U137" s="9" t="n">
-        <v>0</v>
+      <c r="U137" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V137" s="9" t="n">
         <v>0</v>
@@ -16061,7 +16061,7 @@
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -16104,8 +16104,8 @@
       <c r="P149" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q149" s="9" t="n">
-        <v>1</v>
+      <c r="Q149" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R149" s="9" t="n">
         <v>0</v>
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -16937,8 +16937,8 @@
       <c r="S157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T157" s="9" t="n">
-        <v>0</v>
+      <c r="T157" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U157" s="9" t="n">
         <v>0</v>
@@ -17250,7 +17250,7 @@
         <v>0</v>
       </c>
       <c r="S160" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T160" s="9" t="n">
         <v>0</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="P164" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q164" s="9" t="n">
         <v>0</v>
@@ -19181,13 +19181,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>0</v>
       </c>
       <c r="S180" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T180" s="10" t="n">
         <v>1</v>
@@ -19445,7 +19445,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -19478,13 +19478,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -19610,7 +19610,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -19676,7 +19676,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -19742,7 +19742,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -20105,7 +20105,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
@@ -20303,7 +20303,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -20402,7 +20402,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -20435,7 +20435,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
